--- a/ТАУ_оцифровка_методов.xlsx
+++ b/ТАУ_оцифровка_методов.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\ТАУ курсовой\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4D28885-3F59-4EF5-9B8F-4733899894C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF0DB417-080A-44B2-AF2A-042CBEC7E3A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{DFD8D8CC-A9EF-478B-9DD8-548D0E794365}"/>
   </bookViews>
@@ -2289,7 +2289,17 @@
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0599599344934944E-2"/>
+          <c:y val="5.0794154595751026E-2"/>
+          <c:w val="0.82604637639335587"/>
+          <c:h val="0.93230515016311943"/>
+        </c:manualLayout>
+      </c:layout>
       <c:lineChart>
         <c:grouping val="standard"/>
         <c:varyColors val="0"/>
@@ -6686,16 +6696,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>504008</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>185353</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>118654</xdr:rowOff>
+      <xdr:rowOff>146363</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>199208</xdr:colOff>
+      <xdr:colOff>490153</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>118654</xdr:rowOff>
+      <xdr:rowOff>146363</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -6836,10 +6846,10 @@
       <xdr:rowOff>98291</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>198119</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>65634</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>407019</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>83127</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7164,10 +7174,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF2588F3-46EC-43BA-BE21-CEDC05EB84FA}">
-  <dimension ref="A1:AK181"/>
+  <dimension ref="A1:K181"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>0</v>
       </c>
@@ -7192,23 +7202,8 @@
       <c r="K1">
         <v>0</v>
       </c>
-      <c r="L1">
-        <v>0</v>
-      </c>
-      <c r="AF1">
-        <v>126.8</v>
-      </c>
-      <c r="AG1">
-        <v>0.91900000000000004</v>
-      </c>
-      <c r="AJ1">
-        <v>101.5</v>
-      </c>
-      <c r="AK1">
-        <v>0.92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -7233,23 +7228,8 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="AF2">
-        <v>111.1</v>
-      </c>
-      <c r="AG2">
-        <v>0.876</v>
-      </c>
-      <c r="AJ2">
-        <v>132.80000000000001</v>
-      </c>
-      <c r="AK2">
-        <v>0.97399999999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -7274,23 +7254,8 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>142.5</v>
-      </c>
-      <c r="AG3">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="AJ3">
-        <v>136.5</v>
-      </c>
-      <c r="AK3">
-        <v>0.88400000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -7315,23 +7280,8 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>117.2</v>
-      </c>
-      <c r="AG4">
-        <v>0.95399999999999996</v>
-      </c>
-      <c r="AJ4">
-        <v>120.9</v>
-      </c>
-      <c r="AK4">
-        <v>0.83699999999999997</v>
-      </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -7356,23 +7306,8 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="AF5">
-        <v>101.5</v>
-      </c>
-      <c r="AG5">
-        <v>0.92</v>
-      </c>
-      <c r="AJ5">
-        <v>152.30000000000001</v>
-      </c>
-      <c r="AK5">
-        <v>0.91900000000000004</v>
-      </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -7397,23 +7332,8 @@
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="AF6">
-        <v>132.80000000000001</v>
-      </c>
-      <c r="AG6">
-        <v>0.97399999999999998</v>
-      </c>
-      <c r="AJ6">
-        <v>126.8</v>
-      </c>
-      <c r="AK6">
-        <v>0.92100000000000004</v>
-      </c>
-    </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -7438,23 +7358,8 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="AF7">
-        <v>136.5</v>
-      </c>
-      <c r="AG7">
-        <v>0.88400000000000001</v>
-      </c>
-      <c r="AJ7">
-        <v>111.1</v>
-      </c>
-      <c r="AK7">
-        <v>0.88100000000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -7479,23 +7384,8 @@
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="AF8">
-        <v>120.9</v>
-      </c>
-      <c r="AG8">
-        <v>0.83699999999999997</v>
-      </c>
-      <c r="AJ8">
-        <v>142.5</v>
-      </c>
-      <c r="AK8">
-        <v>0.94899999999999995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -7520,23 +7410,8 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="AF9">
-        <v>152.30000000000001</v>
-      </c>
-      <c r="AG9">
-        <v>0.91900000000000004</v>
-      </c>
-      <c r="AJ9">
-        <v>117.2</v>
-      </c>
-      <c r="AK9">
-        <v>0.95499999999999996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -7561,23 +7436,8 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="AF10">
-        <v>126.8</v>
-      </c>
-      <c r="AG10">
-        <v>0.92100000000000004</v>
-      </c>
-      <c r="AJ10">
-        <v>101.5</v>
-      </c>
-      <c r="AK10">
-        <v>0.92100000000000004</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -7602,23 +7462,8 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>111.1</v>
-      </c>
-      <c r="AG11">
-        <v>0.88100000000000001</v>
-      </c>
-      <c r="AJ11">
-        <v>132.80000000000001</v>
-      </c>
-      <c r="AK11">
-        <v>0.97399999999999998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -7643,23 +7488,8 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="AF12">
-        <v>142.5</v>
-      </c>
-      <c r="AG12">
-        <v>0.94899999999999995</v>
-      </c>
-      <c r="AJ12">
-        <v>136.5</v>
-      </c>
-      <c r="AK12">
-        <v>0.88800000000000001</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -7684,23 +7514,8 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>117.2</v>
-      </c>
-      <c r="AG13">
-        <v>0.95499999999999996</v>
-      </c>
-      <c r="AJ13">
-        <v>120.9</v>
-      </c>
-      <c r="AK13">
-        <v>0.84399999999999997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -7725,23 +7540,8 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <v>101.5</v>
-      </c>
-      <c r="AG14">
-        <v>0.92100000000000004</v>
-      </c>
-      <c r="AJ14">
-        <v>152.30000000000001</v>
-      </c>
-      <c r="AK14">
-        <v>0.92100000000000004</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -7766,23 +7566,8 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="AF15">
-        <v>132.80000000000001</v>
-      </c>
-      <c r="AG15">
-        <v>0.97399999999999998</v>
-      </c>
-      <c r="AJ15">
-        <v>126.8</v>
-      </c>
-      <c r="AK15">
-        <v>0.91800000000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -7807,23 +7592,8 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="AF16">
-        <v>136.5</v>
-      </c>
-      <c r="AG16">
-        <v>0.88800000000000001</v>
-      </c>
-      <c r="AJ16">
-        <v>111.1</v>
-      </c>
-      <c r="AK16">
-        <v>0.873</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -7848,23 +7618,8 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="AF17">
-        <v>120.9</v>
-      </c>
-      <c r="AG17">
-        <v>0.84399999999999997</v>
-      </c>
-      <c r="AJ17">
-        <v>142.5</v>
-      </c>
-      <c r="AK17">
-        <v>0.94799999999999995</v>
-      </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -7889,23 +7644,8 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="AF18">
-        <v>152.30000000000001</v>
-      </c>
-      <c r="AG18">
-        <v>0.92100000000000004</v>
-      </c>
-      <c r="AJ18">
-        <v>117.2</v>
-      </c>
-      <c r="AK18">
-        <v>0.95399999999999996</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -7930,23 +7670,8 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="AF19">
-        <v>126.8</v>
-      </c>
-      <c r="AG19">
-        <v>0.91800000000000004</v>
-      </c>
-      <c r="AJ19">
-        <v>101.5</v>
-      </c>
-      <c r="AK19">
-        <v>0.91800000000000004</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -7971,17 +7696,8 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="AF20">
-        <v>111.1</v>
-      </c>
-      <c r="AG20">
-        <v>0.873</v>
-      </c>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -8006,17 +7722,8 @@
       <c r="K21">
         <v>0</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>142.5</v>
-      </c>
-      <c r="AG21">
-        <v>0.94799999999999995</v>
-      </c>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -8041,17 +7748,8 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="AF22">
-        <v>117.2</v>
-      </c>
-      <c r="AG22">
-        <v>0.95399999999999996</v>
-      </c>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -8076,17 +7774,8 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="AF23">
-        <v>101.5</v>
-      </c>
-      <c r="AG23">
-        <v>0.91800000000000004</v>
-      </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -8111,17 +7800,8 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="AF24">
-        <v>132.80000000000001</v>
-      </c>
-      <c r="AG24">
-        <v>0.97399999999999998</v>
-      </c>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -8146,17 +7826,8 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="AF25">
-        <v>136.5</v>
-      </c>
-      <c r="AG25">
-        <v>0.88200000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -8181,17 +7852,8 @@
       <c r="K26">
         <v>0</v>
       </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="AF26">
-        <v>120.9</v>
-      </c>
-      <c r="AG26">
-        <v>0.83199999999999996</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -8216,17 +7878,8 @@
       <c r="K27">
         <v>0</v>
       </c>
-      <c r="L27">
-        <v>0</v>
-      </c>
-      <c r="AF27">
-        <v>152.30000000000001</v>
-      </c>
-      <c r="AG27">
-        <v>0.91800000000000004</v>
-      </c>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -8251,11 +7904,8 @@
       <c r="K28">
         <v>0</v>
       </c>
-      <c r="L28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -8280,11 +7930,8 @@
       <c r="K29">
         <v>0.1</v>
       </c>
-      <c r="L29">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -8309,11 +7956,8 @@
       <c r="K30">
         <v>0.2</v>
       </c>
-      <c r="L30">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -8338,11 +7982,8 @@
       <c r="K31">
         <v>0.4</v>
       </c>
-      <c r="L31">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.3">
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -8367,11 +8008,8 @@
       <c r="K32">
         <v>0.6</v>
       </c>
-      <c r="L32">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -8396,11 +8034,8 @@
       <c r="K33">
         <v>0.8</v>
       </c>
-      <c r="L33">
-        <v>1.4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -8425,11 +8060,8 @@
       <c r="K34">
         <v>1</v>
       </c>
-      <c r="L34">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -8454,11 +8086,8 @@
       <c r="K35">
         <v>1.2</v>
       </c>
-      <c r="L35">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -8483,11 +8112,8 @@
       <c r="K36">
         <v>1.4</v>
       </c>
-      <c r="L36">
-        <v>2.1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -8512,11 +8138,8 @@
       <c r="K37">
         <v>1.6</v>
       </c>
-      <c r="L37">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -8541,11 +8164,8 @@
       <c r="K38">
         <v>1.8</v>
       </c>
-      <c r="L38">
-        <v>2.2999999999999998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -8570,11 +8190,8 @@
       <c r="K39">
         <v>1.9</v>
       </c>
-      <c r="L39">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -8599,11 +8216,8 @@
       <c r="K40">
         <v>2.1</v>
       </c>
-      <c r="L40">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -8628,11 +8242,8 @@
       <c r="K41">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L41">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -8657,11 +8268,8 @@
       <c r="K42">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L42">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -8686,11 +8294,8 @@
       <c r="K43">
         <v>2.4</v>
       </c>
-      <c r="L43">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -8715,11 +8320,8 @@
       <c r="K44">
         <v>2.4</v>
       </c>
-      <c r="L44">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -8744,11 +8346,8 @@
       <c r="K45">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L45">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -8773,11 +8372,8 @@
       <c r="K46">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -8802,11 +8398,8 @@
       <c r="K47">
         <v>2</v>
       </c>
-      <c r="L47">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -8831,11 +8424,8 @@
       <c r="K48">
         <v>1.7</v>
       </c>
-      <c r="L48">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -8860,11 +8450,8 @@
       <c r="K49">
         <v>1.4</v>
       </c>
-      <c r="L49">
-        <v>-1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -8889,11 +8476,8 @@
       <c r="K50">
         <v>1</v>
       </c>
-      <c r="L50">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -8918,11 +8502,8 @@
       <c r="K51">
         <v>0.6</v>
       </c>
-      <c r="L51">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -8947,11 +8528,8 @@
       <c r="K52">
         <v>0.1</v>
       </c>
-      <c r="L52">
-        <v>-3.6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -8976,11 +8554,8 @@
       <c r="K53">
         <v>-0.4</v>
       </c>
-      <c r="L53">
-        <v>-4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -9005,11 +8580,8 @@
       <c r="K54">
         <v>-0.9</v>
       </c>
-      <c r="L54">
-        <v>-5.0999999999999996</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -9034,11 +8606,8 @@
       <c r="K55">
         <v>-1.5</v>
       </c>
-      <c r="L55">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -9063,11 +8632,8 @@
       <c r="K56">
         <v>-2.1</v>
       </c>
-      <c r="L56">
-        <v>-6.1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -9092,11 +8658,8 @@
       <c r="K57">
         <v>-2.7</v>
       </c>
-      <c r="L57">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -9121,11 +8684,8 @@
       <c r="K58">
         <v>-3.3</v>
       </c>
-      <c r="L58">
-        <v>-6.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -9150,11 +8710,8 @@
       <c r="K59">
         <v>-3.9</v>
       </c>
-      <c r="L59">
-        <v>-6.3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -9179,11 +8736,8 @@
       <c r="K60">
         <v>-4.4000000000000004</v>
       </c>
-      <c r="L60">
-        <v>-6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -9208,11 +8762,8 @@
       <c r="K61">
         <v>-4.9000000000000004</v>
       </c>
-      <c r="L61">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -9237,11 +8788,8 @@
       <c r="K62">
         <v>-5.3</v>
       </c>
-      <c r="L62">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -9266,11 +8814,8 @@
       <c r="K63">
         <v>-5.7</v>
       </c>
-      <c r="L63">
-        <v>-4</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -9295,11 +8840,8 @@
       <c r="K64">
         <v>-6</v>
       </c>
-      <c r="L64">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -9324,11 +8866,8 @@
       <c r="K65">
         <v>-6.2</v>
       </c>
-      <c r="L65">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -9353,11 +8892,8 @@
       <c r="K66">
         <v>-6.3</v>
       </c>
-      <c r="L66">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -9382,11 +8918,8 @@
       <c r="K67">
         <v>-6.4</v>
       </c>
-      <c r="L67">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -9411,11 +8944,8 @@
       <c r="K68">
         <v>-6.3</v>
       </c>
-      <c r="L68">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -9440,11 +8970,8 @@
       <c r="K69">
         <v>-6.2</v>
       </c>
-      <c r="L69">
-        <v>3.4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -9469,11 +8996,8 @@
       <c r="K70">
         <v>-6</v>
       </c>
-      <c r="L70">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -9498,11 +9022,8 @@
       <c r="K71">
         <v>-5.7</v>
       </c>
-      <c r="L71">
-        <v>6.7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -9527,11 +9048,8 @@
       <c r="K72">
         <v>-5.3</v>
       </c>
-      <c r="L72">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -9556,11 +9074,8 @@
       <c r="K73">
         <v>-4.8</v>
       </c>
-      <c r="L73">
-        <v>10.1</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -9585,11 +9100,8 @@
       <c r="K74">
         <v>-4.2</v>
       </c>
-      <c r="L74">
-        <v>11.7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -9614,11 +9126,8 @@
       <c r="K75">
         <v>-3.5</v>
       </c>
-      <c r="L75">
-        <v>13.1</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -9643,11 +9152,8 @@
       <c r="K76">
         <v>-2.8</v>
       </c>
-      <c r="L76">
-        <v>14.3</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -9672,11 +9178,8 @@
       <c r="K77">
         <v>-2</v>
       </c>
-      <c r="L77">
-        <v>15.1</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -9701,11 +9204,8 @@
       <c r="K78">
         <v>-1.2</v>
       </c>
-      <c r="L78">
-        <v>15.6</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -9730,11 +9230,8 @@
       <c r="K79">
         <v>-0.3</v>
       </c>
-      <c r="L79">
-        <v>15.9</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -9759,11 +9256,8 @@
       <c r="K80">
         <v>0.6</v>
       </c>
-      <c r="L80">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -9788,11 +9282,8 @@
       <c r="K81">
         <v>1.6</v>
       </c>
-      <c r="L81">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -9817,11 +9308,8 @@
       <c r="K82">
         <v>2.6</v>
       </c>
-      <c r="L82">
-        <v>15.8</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -9846,11 +9334,8 @@
       <c r="K83">
         <v>3.7</v>
       </c>
-      <c r="L83">
-        <v>15.3</v>
-      </c>
-    </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -9875,11 +9360,8 @@
       <c r="K84">
         <v>4.9000000000000004</v>
       </c>
-      <c r="L84">
-        <v>14.5</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -9904,11 +9386,8 @@
       <c r="K85">
         <v>6.1</v>
       </c>
-      <c r="L85">
-        <v>13.4</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -9933,11 +9412,8 @@
       <c r="K86">
         <v>7.4</v>
       </c>
-      <c r="L86">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -9962,11 +9438,8 @@
       <c r="K87">
         <v>8.6999999999999993</v>
       </c>
-      <c r="L87">
-        <v>10.3</v>
-      </c>
-    </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -9991,11 +9464,8 @@
       <c r="K88">
         <v>10</v>
       </c>
-      <c r="L88">
-        <v>8.3000000000000007</v>
-      </c>
-    </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -10020,11 +9490,8 @@
       <c r="K89">
         <v>11.3</v>
       </c>
-      <c r="L89">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -10049,11 +9516,8 @@
       <c r="K90">
         <v>12.5</v>
       </c>
-      <c r="L90">
-        <v>3.5</v>
-      </c>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -10078,11 +9542,8 @@
       <c r="K91">
         <v>13.6</v>
       </c>
-      <c r="L91">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -10104,11 +9565,8 @@
       <c r="K92">
         <v>14.6</v>
       </c>
-      <c r="L92">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -10130,11 +9588,8 @@
       <c r="K93">
         <v>15.2</v>
       </c>
-      <c r="L93">
-        <v>-4.8</v>
-      </c>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -10156,11 +9611,8 @@
       <c r="K94">
         <v>15.7</v>
       </c>
-      <c r="L94">
-        <v>-7.2</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -10182,11 +9634,8 @@
       <c r="K95">
         <v>15.9</v>
       </c>
-      <c r="L95">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -10205,11 +9654,8 @@
       <c r="K96">
         <v>16</v>
       </c>
-      <c r="L96">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -10225,11 +9671,8 @@
       <c r="K97">
         <v>16</v>
       </c>
-      <c r="L97">
-        <v>-10.5</v>
-      </c>
-    </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -10245,11 +9688,8 @@
       <c r="K98">
         <v>15.8</v>
       </c>
-      <c r="L98">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -10265,11 +9705,8 @@
       <c r="K99">
         <v>15.5</v>
       </c>
-      <c r="L99">
-        <v>-9</v>
-      </c>
-    </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -10285,11 +9722,8 @@
       <c r="K100">
         <v>14.9</v>
       </c>
-      <c r="L100">
-        <v>-7.5</v>
-      </c>
-    </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -10305,11 +9739,8 @@
       <c r="K101">
         <v>14.2</v>
       </c>
-      <c r="L101">
-        <v>-5.5</v>
-      </c>
-    </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -10325,11 +9756,8 @@
       <c r="K102">
         <v>13.2</v>
       </c>
-      <c r="L102">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -10345,11 +9773,8 @@
       <c r="K103">
         <v>12</v>
       </c>
-      <c r="L103">
-        <v>-0.5</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -10365,11 +9790,8 @@
       <c r="K104">
         <v>10.6</v>
       </c>
-      <c r="L104">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -10385,11 +9807,8 @@
       <c r="K105">
         <v>9</v>
       </c>
-      <c r="L105">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -10405,11 +9824,8 @@
       <c r="K106">
         <v>7.2</v>
       </c>
-      <c r="L106">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -10425,11 +9841,8 @@
       <c r="K107">
         <v>5.3</v>
       </c>
-      <c r="L107">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -10445,11 +9858,8 @@
       <c r="K108">
         <v>3.3</v>
       </c>
-      <c r="L108">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -10465,11 +9875,8 @@
       <c r="K109">
         <v>1.2</v>
       </c>
-      <c r="L109">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -10485,11 +9892,8 @@
       <c r="K110">
         <v>-1</v>
       </c>
-      <c r="L110">
-        <v>9.5</v>
-      </c>
-    </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G111">
         <v>110</v>
       </c>
@@ -10499,11 +9903,8 @@
       <c r="K111">
         <v>-3.2</v>
       </c>
-      <c r="L111">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="G112">
         <v>111</v>
       </c>
@@ -10513,11 +9914,8 @@
       <c r="K112">
         <v>-5.3</v>
       </c>
-      <c r="L112">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="113" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="113" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G113">
         <v>112</v>
       </c>
@@ -10527,11 +9925,8 @@
       <c r="K113">
         <v>-7.1</v>
       </c>
-      <c r="L113">
-        <v>6.5</v>
-      </c>
-    </row>
-    <row r="114" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="114" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G114">
         <v>113</v>
       </c>
@@ -10541,11 +9936,8 @@
       <c r="K114">
         <v>-8.6</v>
       </c>
-      <c r="L114">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="115" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="115" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G115">
         <v>114</v>
       </c>
@@ -10555,11 +9947,8 @@
       <c r="K115">
         <v>-9.8000000000000007</v>
       </c>
-      <c r="L115">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="116" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="116" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G116">
         <v>115</v>
       </c>
@@ -10569,11 +9958,8 @@
       <c r="K116">
         <v>-10.5</v>
       </c>
-      <c r="L116">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="117" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="117" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G117">
         <v>116</v>
       </c>
@@ -10583,11 +9969,8 @@
       <c r="K117">
         <v>-10.9</v>
       </c>
-      <c r="L117">
-        <v>-4.5</v>
-      </c>
-    </row>
-    <row r="118" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="118" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G118">
         <v>117</v>
       </c>
@@ -10597,11 +9980,8 @@
       <c r="K118">
         <v>-10.8</v>
       </c>
-      <c r="L118">
-        <v>-8</v>
-      </c>
-    </row>
-    <row r="119" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="119" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G119">
         <v>118</v>
       </c>
@@ -10611,11 +9991,8 @@
       <c r="K119">
         <v>-10.3</v>
       </c>
-      <c r="L119">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="120" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="120" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G120">
         <v>119</v>
       </c>
@@ -10625,11 +10002,8 @@
       <c r="K120">
         <v>-9.5</v>
       </c>
-      <c r="L120">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="121" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="121" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G121">
         <v>120</v>
       </c>
@@ -10639,11 +10013,8 @@
       <c r="K121">
         <v>-8.5</v>
       </c>
-      <c r="L121">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="122" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="122" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G122">
         <v>121</v>
       </c>
@@ -10653,11 +10024,8 @@
       <c r="K122">
         <v>-7.2</v>
       </c>
-      <c r="L122">
-        <v>-14.5</v>
-      </c>
-    </row>
-    <row r="123" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="123" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G123">
         <v>122</v>
       </c>
@@ -10667,11 +10035,8 @@
       <c r="K123">
         <v>-5.8</v>
       </c>
-      <c r="L123">
-        <v>-14.5</v>
-      </c>
-    </row>
-    <row r="124" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="124" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G124">
         <v>123</v>
       </c>
@@ -10681,11 +10046,8 @@
       <c r="K124">
         <v>-4.2</v>
       </c>
-      <c r="L124">
-        <v>-14</v>
-      </c>
-    </row>
-    <row r="125" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="125" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G125">
         <v>124</v>
       </c>
@@ -10695,11 +10057,8 @@
       <c r="K125">
         <v>-2.5</v>
       </c>
-      <c r="L125">
-        <v>-13</v>
-      </c>
-    </row>
-    <row r="126" spans="7:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="126" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G126">
         <v>125</v>
       </c>
@@ -10710,7 +10069,7 @@
         <v>-0.8</v>
       </c>
     </row>
-    <row r="127" spans="7:12" x14ac:dyDescent="0.3">
+    <row r="127" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G127">
         <v>126</v>
       </c>
@@ -10721,7 +10080,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="128" spans="7:12" x14ac:dyDescent="0.3">
+    <row r="128" spans="7:11" x14ac:dyDescent="0.3">
       <c r="G128">
         <v>127</v>
       </c>
